--- a/data/trans_orig/P36B08_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148531</t>
+          <t>150335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181414</t>
+          <t>182830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169701</t>
+          <t>170774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>200317</t>
+          <t>199580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330254</t>
+          <t>329315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>375450</t>
+          <t>372772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90762</t>
+          <t>89346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123645</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>61258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91137</t>
+          <t>90064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157564</t>
+          <t>160242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202760</t>
+          <t>203699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202274</t>
+          <t>200774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>246203</t>
+          <t>247549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>266518</t>
+          <t>270262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>312387</t>
+          <t>313017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>485834</t>
+          <t>483992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>546645</t>
+          <t>548796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>246872</t>
+          <t>245526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>290801</t>
+          <t>292301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191562</t>
+          <t>190932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237431</t>
+          <t>233687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>450379</t>
+          <t>448228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>511190</t>
+          <t>513032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>216291</t>
+          <t>214830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>248343</t>
+          <t>245637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>241889</t>
+          <t>241049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>273067</t>
+          <t>272968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>468847</t>
+          <t>467470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511534</t>
+          <t>511968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70503</t>
+          <t>73209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102555</t>
+          <t>104016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62345</t>
+          <t>62444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93523</t>
+          <t>94363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142724</t>
+          <t>142290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185411</t>
+          <t>186788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>227669</t>
+          <t>225925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261735</t>
+          <t>261687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>272951</t>
+          <t>273019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303135</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>511831</t>
+          <t>509158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>556774</t>
+          <t>556998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96936</t>
+          <t>96984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131002</t>
+          <t>132746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68321</t>
+          <t>68199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98505</t>
+          <t>98437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173353</t>
+          <t>173129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218296</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89155</t>
+          <t>87835</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117889</t>
+          <t>116987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115803</t>
+          <t>114130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143825</t>
+          <t>144506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212776</t>
+          <t>213085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253766</t>
+          <t>252342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85419</t>
+          <t>86321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>115473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63843</t>
+          <t>63162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91865</t>
+          <t>93538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>157210</t>
+          <t>158634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198200</t>
+          <t>197891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159385</t>
+          <t>158177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>190022</t>
+          <t>189556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196687</t>
+          <t>197577</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>226245</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>361842</t>
+          <t>364130</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>407190</t>
+          <t>406773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80789</t>
+          <t>81255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111426</t>
+          <t>112634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52894</t>
+          <t>51899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81457</t>
+          <t>80567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141765</t>
+          <t>142182</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187113</t>
+          <t>184825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>442942</t>
+          <t>443475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>487182</t>
+          <t>485422</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>454168</t>
+          <t>455915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>499048</t>
+          <t>498827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>909157</t>
+          <t>912491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>974382</t>
+          <t>972457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127845</t>
+          <t>129605</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>172085</t>
+          <t>171552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139171</t>
+          <t>139392</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184051</t>
+          <t>182304</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278864</t>
+          <t>280789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>344089</t>
+          <t>340755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>429874</t>
+          <t>434095</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>486232</t>
+          <t>486339</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>532505</t>
+          <t>529833</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>582206</t>
+          <t>583163</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>975880</t>
+          <t>979636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1053693</t>
+          <t>1054132</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>257563</t>
+          <t>257456</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>313921</t>
+          <t>309700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>200245</t>
+          <t>199288</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>249946</t>
+          <t>252618</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>472553</t>
+          <t>472114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>550366</t>
+          <t>546610</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2013745</t>
+          <t>2020508</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2128375</t>
+          <t>2125928</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2341215</t>
+          <t>2344836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2449848</t>
+          <t>2451375</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4397999</t>
+          <t>4385114</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4555090</t>
+          <t>4542259</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1147334</t>
+          <t>1149781</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1261964</t>
+          <t>1255201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>928289</t>
+          <t>926762</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1036922</t>
+          <t>1033301</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2098757</t>
+          <t>2111588</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2255848</t>
+          <t>2268733</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193818</t>
+          <t>192592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224488</t>
+          <t>224227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>209178</t>
+          <t>209709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238475</t>
+          <t>239632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>413419</t>
+          <t>411902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455081</t>
+          <t>454830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70250</t>
+          <t>70511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100920</t>
+          <t>102146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>75492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124858</t>
+          <t>125109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166520</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>262027</t>
+          <t>259818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306782</t>
+          <t>306529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>329004</t>
+          <t>331414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>373970</t>
+          <t>374159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>603440</t>
+          <t>602568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>667555</t>
+          <t>667788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198745</t>
+          <t>198998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243500</t>
+          <t>245709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149795</t>
+          <t>149606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194761</t>
+          <t>192351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361737</t>
+          <t>361504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425852</t>
+          <t>426724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>244935</t>
+          <t>242659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272376</t>
+          <t>270386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278513</t>
+          <t>278797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>304928</t>
+          <t>305644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>529781</t>
+          <t>530788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>569480</t>
+          <t>569180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50642</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78083</t>
+          <t>80359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36092</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62223</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94558</t>
+          <t>94858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134257</t>
+          <t>133250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>274727</t>
+          <t>273009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>309142</t>
+          <t>308038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>317101</t>
+          <t>317424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>344660</t>
+          <t>346140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>601823</t>
+          <t>603530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>645735</t>
+          <t>647133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>65944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99255</t>
+          <t>100973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44291</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71850</t>
+          <t>71527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117198</t>
+          <t>115800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161110</t>
+          <t>159403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120873</t>
+          <t>121052</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149985</t>
+          <t>149803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146294</t>
+          <t>146150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173315</t>
+          <t>172171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>278821</t>
+          <t>272490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317476</t>
+          <t>314342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62633</t>
+          <t>62815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91745</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>73441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114733</t>
+          <t>117867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153388</t>
+          <t>159719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>183879</t>
+          <t>181493</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>212239</t>
+          <t>213771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>217683</t>
+          <t>217904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242720</t>
+          <t>243718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>409724</t>
+          <t>408522</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>449213</t>
+          <t>447336</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61742</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90102</t>
+          <t>92488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>34378</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60413</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102864</t>
+          <t>104741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142353</t>
+          <t>143555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>464055</t>
+          <t>461221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>509374</t>
+          <t>510016</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>543546</t>
+          <t>544522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>586397</t>
+          <t>587590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1022140</t>
+          <t>1020770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1085308</t>
+          <t>1084536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148264</t>
+          <t>147622</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193583</t>
+          <t>196417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102753</t>
+          <t>101560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145604</t>
+          <t>144628</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>261480</t>
+          <t>262252</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>324648</t>
+          <t>326018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>538767</t>
+          <t>537618</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>591875</t>
+          <t>589049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>633393</t>
+          <t>635086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>682550</t>
+          <t>683072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1189150</t>
+          <t>1189789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1256291</t>
+          <t>1258205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>186194</t>
+          <t>189020</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>239302</t>
+          <t>240451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140153</t>
+          <t>139631</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189310</t>
+          <t>187617</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>344481</t>
+          <t>342567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>411622</t>
+          <t>410983</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2376920</t>
+          <t>2378762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2486475</t>
+          <t>2487264</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2772253</t>
+          <t>2770591</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2868338</t>
+          <t>2869215</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5181387</t>
+          <t>5183933</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5330806</t>
+          <t>5328090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>933096</t>
+          <t>932307</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1042651</t>
+          <t>1040809</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>680139</t>
+          <t>679262</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>776224</t>
+          <t>777886</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1637243</t>
+          <t>1639959</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1786662</t>
+          <t>1784116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>220603</t>
+          <t>218086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249757</t>
+          <t>249896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231700</t>
+          <t>232215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257221</t>
+          <t>256634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>459789</t>
+          <t>460070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>498906</t>
+          <t>498690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43062</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>74733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29496</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55017</t>
+          <t>54502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80629</t>
+          <t>80845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119746</t>
+          <t>119465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>317614</t>
+          <t>319244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>359518</t>
+          <t>361344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>390361</t>
+          <t>390316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>428594</t>
+          <t>428427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>721549</t>
+          <t>723206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>775944</t>
+          <t>779016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,5%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138098</t>
+          <t>136272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180002</t>
+          <t>178372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92054</t>
+          <t>92221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130287</t>
+          <t>130332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242320</t>
+          <t>239248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296715</t>
+          <t>295058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215312</t>
+          <t>216431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>247201</t>
+          <t>245946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>246111</t>
+          <t>247832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>275347</t>
+          <t>278481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>469985</t>
+          <t>471139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>515340</t>
+          <t>513134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,47%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70442</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102331</t>
+          <t>101212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60962</t>
+          <t>57828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90198</t>
+          <t>88477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138612</t>
+          <t>140818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>183967</t>
+          <t>182813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280735</t>
+          <t>280510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>311661</t>
+          <t>311525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>321602</t>
+          <t>321067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>348589</t>
+          <t>348408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>611873</t>
+          <t>611549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>652437</t>
+          <t>651807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>58439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89229</t>
+          <t>89454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37736</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>65258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103852</t>
+          <t>104482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144416</t>
+          <t>144740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>179716</t>
+          <t>177758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197595</t>
+          <t>197441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185398</t>
+          <t>185721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203818</t>
+          <t>203992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>372898</t>
+          <t>372612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>397439</t>
+          <t>397688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13626</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>33463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>32866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32369</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56910</t>
+          <t>57196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126455</t>
+          <t>126544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>157920</t>
+          <t>157836</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>146839</t>
+          <t>147359</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179057</t>
+          <t>181528</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>280561</t>
+          <t>281544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327370</t>
+          <t>329259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104192</t>
+          <t>104276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>135568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92965</t>
+          <t>90494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>125183</t>
+          <t>124663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206765</t>
+          <t>204876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253574</t>
+          <t>252591</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>386406</t>
+          <t>387763</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>439405</t>
+          <t>439460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>469511</t>
+          <t>466056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>513321</t>
+          <t>515798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>871849</t>
+          <t>868770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>940154</t>
+          <t>940951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211967</t>
+          <t>211912</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264966</t>
+          <t>263609</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170555</t>
+          <t>168078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>214365</t>
+          <t>217820</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>395094</t>
+          <t>394297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>463399</t>
+          <t>466478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>564153</t>
+          <t>567912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>613606</t>
+          <t>614010</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>601545</t>
+          <t>599907</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>652116</t>
+          <t>650769</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1183296</t>
+          <t>1179155</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1252102</t>
+          <t>1251867</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160819</t>
+          <t>160415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>210272</t>
+          <t>206513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>171185</t>
+          <t>172532</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>221756</t>
+          <t>223394</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>345624</t>
+          <t>345859</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>414430</t>
+          <t>418571</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2389348</t>
+          <t>2392468</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2491913</t>
+          <t>2498647</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2683182</t>
+          <t>2676208</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2780348</t>
+          <t>2778115</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5097210</t>
+          <t>5092834</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5246277</t>
+          <t>5239708</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>885258</t>
+          <t>878524</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>987823</t>
+          <t>984703</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>747436</t>
+          <t>749669</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>844602</t>
+          <t>851576</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1658679</t>
+          <t>1665248</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1807746</t>
+          <t>1812122</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>291388</t>
+          <t>299982</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>273773</t>
+          <t>288372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299916</t>
+          <t>306954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>276740</t>
+          <t>304929</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>259017</t>
+          <t>294478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283524</t>
+          <t>309909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>568127</t>
+          <t>604911</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>545685</t>
+          <t>590479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>580142</t>
+          <t>615191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55392</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>481243</t>
+          <t>494236</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>461493</t>
+          <t>478640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>493210</t>
+          <t>507564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>479967</t>
+          <t>511201</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>468316</t>
+          <t>498887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>488984</t>
+          <t>519616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>961209</t>
+          <t>1005438</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>938487</t>
+          <t>985660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>977164</t>
+          <t>1020762</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37147</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56897</t>
+          <t>52007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46653</t>
+          <t>47607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>72150</t>
+          <t>71703</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56195</t>
+          <t>56379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94872</t>
+          <t>91481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>288586</t>
+          <t>290285</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>277033</t>
+          <t>278906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>297675</t>
+          <t>298711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>328045</t>
+          <t>335656</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>319879</t>
+          <t>326875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>334411</t>
+          <t>341813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>616631</t>
+          <t>625941</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>602415</t>
+          <t>612377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627484</t>
+          <t>635565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39017</t>
+          <t>37087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>46514</t>
+          <t>44374</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60730</t>
+          <t>57938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347095</t>
+          <t>354322</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347095</t>
+          <t>354322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347095</t>
+          <t>354322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663145</t>
+          <t>670315</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663145</t>
+          <t>670315</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663145</t>
+          <t>670315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>306122</t>
+          <t>366680</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298329</t>
+          <t>359638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>309882</t>
+          <t>370343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>468218</t>
+          <t>413471</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>460629</t>
+          <t>405568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>472421</t>
+          <t>417590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>774340</t>
+          <t>780152</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>764559</t>
+          <t>768682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>781085</t>
+          <t>786239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>372377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>372377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>372377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787533</t>
+          <t>794338</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787533</t>
+          <t>794338</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787533</t>
+          <t>794338</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,27 +12069,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>178227</t>
+          <t>205150</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175811</t>
+          <t>202686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>206420</t>
+          <t>224854</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203341</t>
+          <t>221747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207552</t>
+          <t>226057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>384647</t>
+          <t>430005</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381320</t>
+          <t>426222</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386031</t>
+          <t>431645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -12192,12 +12192,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207968</t>
+          <t>226492</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207968</t>
+          <t>226492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207968</t>
+          <t>226492</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386710</t>
+          <t>432157</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386710</t>
+          <t>432157</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386710</t>
+          <t>432157</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>261124</t>
+          <t>262060</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>253627</t>
+          <t>254538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>265368</t>
+          <t>266102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>251492</t>
+          <t>258330</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>244783</t>
+          <t>252169</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>254781</t>
+          <t>261412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>512616</t>
+          <t>520390</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>503836</t>
+          <t>512737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>518224</t>
+          <t>526103</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,22 +12560,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>21720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>545559</t>
+          <t>631741</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522456</t>
+          <t>609316</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>562964</t>
+          <t>651523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>795402</t>
+          <t>709933</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>769098</t>
+          <t>692499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>825109</t>
+          <t>723776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1340961</t>
+          <t>1341674</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1306247</t>
+          <t>1309912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1393192</t>
+          <t>1364521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>76719</t>
+          <t>84742</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59314</t>
+          <t>64960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99822</t>
+          <t>107167</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53863</t>
+          <t>62124</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>48281</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80167</t>
+          <t>79558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>130582</t>
+          <t>146866</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>78351</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>165296</t>
+          <t>178628</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622278</t>
+          <t>716483</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622278</t>
+          <t>716483</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622278</t>
+          <t>716483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471543</t>
+          <t>1488540</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471543</t>
+          <t>1488540</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471543</t>
+          <t>1488540</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>911649</t>
+          <t>779115</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>897380</t>
+          <t>765304</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>922322</t>
+          <t>786736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>701933</t>
+          <t>813584</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>693678</t>
+          <t>803996</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>707404</t>
+          <t>820134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1613582</t>
+          <t>1592699</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1599469</t>
+          <t>1577313</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1627113</t>
+          <t>1603488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928012</t>
+          <t>797351</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928012</t>
+          <t>797351</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928012</t>
+          <t>797351</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716172</t>
+          <t>829598</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716172</t>
+          <t>829598</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716172</t>
+          <t>829598</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644184</t>
+          <t>1626949</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644184</t>
+          <t>1626949</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644184</t>
+          <t>1626949</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3263898</t>
+          <t>3329251</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3225292</t>
+          <t>3298351</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3308458</t>
+          <t>3361511</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3508214</t>
+          <t>3571959</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3481519</t>
+          <t>3547249</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3538720</t>
+          <t>3595058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6772113</t>
+          <t>6901209</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6717872</t>
+          <t>6856932</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6824431</t>
+          <t>6937159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>192468</t>
+          <t>198818</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>231074</t>
+          <t>229718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>149662</t>
+          <t>158776</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>119156</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>183486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>342130</t>
+          <t>357595</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>289812</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>396371</t>
+          <t>401872</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P36B08_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2023 (tasa de respuesta: 99,86%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
